--- a/capitals_enriched (2).xlsx
+++ b/capitals_enriched (2).xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2023</v>
+        <v>9265</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1434</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>877</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>689</v>
+        <v>863</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1364</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>

--- a/capitals_enriched (2).xlsx
+++ b/capitals_enriched (2).xlsx
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9265</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>336</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7982</v>
+        <v>876</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>863</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1045</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
